--- a/data/trans_orig/IP25-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP25-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>84542</t>
+          <t>83774</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>95540</t>
+          <t>95375</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>77024</t>
+          <t>76910</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>87973</t>
+          <t>88132</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>165309</t>
+          <t>164967</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>180192</t>
+          <t>180960</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,96%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8079</t>
+          <t>8244</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19077</t>
+          <t>19845</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9572</t>
+          <t>9413</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20521</t>
+          <t>20635</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20972</t>
+          <t>20204</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35855</t>
+          <t>36197</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,99%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>71548</t>
+          <t>72609</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>81367</t>
+          <t>81549</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>64903</t>
+          <t>64479</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>76190</t>
+          <t>75555</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>139341</t>
+          <t>140349</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>154701</t>
+          <t>155315</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,59%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6022</t>
+          <t>5840</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15841</t>
+          <t>14780</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9780</t>
+          <t>10415</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21067</t>
+          <t>21491</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>18658</t>
+          <t>18044</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>34018</t>
+          <t>33010</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,04%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>55150</t>
+          <t>55408</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63238</t>
+          <t>63361</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>85681</t>
+          <t>85513</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>95209</t>
+          <t>95038</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>144161</t>
+          <t>143537</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>156206</t>
+          <t>155631</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>93,75%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3320</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11531</t>
+          <t>11273</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4123</t>
+          <t>4294</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13651</t>
+          <t>13819</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9807</t>
+          <t>10382</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>21852</t>
+          <t>22476</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,54%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>175930</t>
+          <t>174546</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>188829</t>
+          <t>188227</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>170209</t>
+          <t>171145</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>185398</t>
+          <t>184671</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>350571</t>
+          <t>351043</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>370262</t>
+          <t>370954</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>92,09%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>12506</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24803</t>
+          <t>26187</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16676</t>
+          <t>17403</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>31865</t>
+          <t>30929</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>32545</t>
+          <t>31853</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>52236</t>
+          <t>51764</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>92026</t>
+          <t>92580</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>100360</t>
+          <t>100326</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>104668</t>
+          <t>104267</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>116851</t>
+          <t>116797</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>200024</t>
+          <t>200110</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>214666</t>
+          <t>214830</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,84%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3760</t>
+          <t>3794</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12094</t>
+          <t>11540</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10438</t>
+          <t>10492</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22621</t>
+          <t>23022</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16744</t>
+          <t>16580</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>31386</t>
+          <t>31300</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,53%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>64018</t>
+          <t>64468</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>72016</t>
+          <t>71753</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>61048</t>
+          <t>60858</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>68912</t>
+          <t>68965</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>127184</t>
+          <t>127768</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>139653</t>
+          <t>139435</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,68%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2854</t>
+          <t>3117</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10852</t>
+          <t>10402</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3480</t>
+          <t>3427</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11344</t>
+          <t>11534</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>7609</t>
+          <t>7827</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20078</t>
+          <t>19494</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,24%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>564286</t>
+          <t>563948</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>587975</t>
+          <t>587526</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>585939</t>
+          <t>584429</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>613042</t>
+          <t>612073</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1157407</t>
+          <t>1158146</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1193433</t>
+          <t>1193323</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>49437</t>
+          <t>49886</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>73126</t>
+          <t>73464</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>71561</t>
+          <t>72530</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>98664</t>
+          <t>100174</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>128582</t>
+          <t>128692</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>164608</t>
+          <t>163869</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,4%</t>
         </is>
       </c>
     </row>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>74922</t>
+          <t>74965</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>84514</t>
+          <t>84531</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>74998</t>
+          <t>74525</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>84093</t>
+          <t>84071</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>152773</t>
+          <t>153070</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>166153</t>
+          <t>166574</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>93,08%</t>
         </is>
       </c>
     </row>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5419</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15011</t>
+          <t>14968</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4923</t>
+          <t>4945</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14018</t>
+          <t>14491</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12797</t>
+          <t>12376</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26177</t>
+          <t>25880</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,46%</t>
         </is>
       </c>
     </row>
@@ -3710,12 +3710,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>78178</t>
+          <t>77707</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>87212</t>
+          <t>87475</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>80763</t>
+          <t>81289</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>90950</t>
+          <t>91268</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>162559</t>
+          <t>162401</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>176260</t>
+          <t>176315</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,78%</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6054</t>
+          <t>5791</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15088</t>
+          <t>15559</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5828</t>
+          <t>5510</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16015</t>
+          <t>15489</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>13784</t>
+          <t>13729</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>27485</t>
+          <t>27643</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,55%</t>
         </is>
       </c>
     </row>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>72645</t>
+          <t>72697</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>81487</t>
+          <t>82011</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>71770</t>
+          <t>71651</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>81586</t>
+          <t>81492</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4103,12 +4103,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>148910</t>
+          <t>148237</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>161530</t>
+          <t>161824</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,87%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4670</t>
+          <t>4146</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13512</t>
+          <t>13460</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4657</t>
+          <t>4751</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14473</t>
+          <t>14592</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10870</t>
+          <t>10576</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>23490</t>
+          <t>24163</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>14,02%</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>169342</t>
+          <t>169619</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>185836</t>
+          <t>185930</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>203223</t>
+          <t>203688</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>216575</t>
+          <t>216868</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>379092</t>
+          <t>379045</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>399347</t>
+          <t>399736</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,27%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20272</t>
+          <t>20178</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36766</t>
+          <t>36489</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10546</t>
+          <t>10253</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23898</t>
+          <t>23433</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>33882</t>
+          <t>33493</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>54137</t>
+          <t>54184</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,51%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>123944</t>
+          <t>123157</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>136557</t>
+          <t>136307</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>119838</t>
+          <t>118917</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>132202</t>
+          <t>131796</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>248504</t>
+          <t>248320</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>265855</t>
+          <t>266397</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,29%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11671</t>
+          <t>11921</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24284</t>
+          <t>25071</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8208</t>
+          <t>8614</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20572</t>
+          <t>21493</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>22783</t>
+          <t>22241</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>40134</t>
+          <t>40318</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,97%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44438</t>
+          <t>44534</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>51376</t>
+          <t>51417</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>61620</t>
+          <t>61200</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>69935</t>
+          <t>70069</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>108701</t>
+          <t>108576</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>119884</t>
+          <t>119917</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,72%</t>
         </is>
       </c>
     </row>
@@ -5195,12 +5195,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>2494</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9473</t>
+          <t>9377</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4103</t>
+          <t>3969</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12418</t>
+          <t>12838</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8065</t>
+          <t>8032</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>19248</t>
+          <t>19373</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,14%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>586162</t>
+          <t>585318</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>612749</t>
+          <t>611969</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>635912</t>
+          <t>635965</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>661865</t>
+          <t>661118</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1229543</t>
+          <t>1230032</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1267704</t>
+          <t>1267351</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>91,1%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>64853</t>
+          <t>65633</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>91440</t>
+          <t>92284</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>51743</t>
+          <t>52490</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>77696</t>
+          <t>77643</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>123506</t>
+          <t>123859</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>161667</t>
+          <t>161178</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,59%</t>
         </is>
       </c>
     </row>
@@ -6002,12 +6002,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>65421</t>
+          <t>64987</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>76104</t>
+          <t>75828</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>79837</t>
+          <t>79442</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>91306</t>
+          <t>91039</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6072,12 +6072,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>149200</t>
+          <t>148877</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>164483</t>
+          <t>164277</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,82%</t>
         </is>
       </c>
     </row>
@@ -6115,12 +6115,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6986</t>
+          <t>7262</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17669</t>
+          <t>18103</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8491</t>
+          <t>8758</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19960</t>
+          <t>20355</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18404</t>
+          <t>18610</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33687</t>
+          <t>34010</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,6%</t>
         </is>
       </c>
     </row>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>88700</t>
+          <t>88126</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>98999</t>
+          <t>98597</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>97658</t>
+          <t>97057</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>107077</t>
+          <t>107126</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>189690</t>
+          <t>189262</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>203550</t>
+          <t>203285</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,05%</t>
         </is>
       </c>
     </row>
@@ -6458,12 +6458,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6715</t>
+          <t>7117</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17014</t>
+          <t>17588</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5669</t>
+          <t>5620</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15088</t>
+          <t>15689</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>14910</t>
+          <t>15175</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>28770</t>
+          <t>29198</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,37%</t>
         </is>
       </c>
     </row>
@@ -6688,12 +6688,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>52757</t>
+          <t>52867</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>59537</t>
+          <t>59505</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>63090</t>
+          <t>62469</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>71573</t>
+          <t>71549</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6758,12 +6758,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>118789</t>
+          <t>118381</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>129365</t>
+          <t>129361</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6773,7 +6773,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -6801,12 +6801,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9083</t>
+          <t>8973</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6836,12 +6836,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3855</t>
+          <t>3879</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12338</t>
+          <t>12959</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6871,12 +6871,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7903</t>
+          <t>7907</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18479</t>
+          <t>18887</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,76%</t>
         </is>
       </c>
     </row>
@@ -7031,12 +7031,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>194967</t>
+          <t>195412</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>208244</t>
+          <t>209276</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>188421</t>
+          <t>188164</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>200705</t>
+          <t>200795</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>387463</t>
+          <t>388171</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>407026</t>
+          <t>406454</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,56%</t>
         </is>
       </c>
     </row>
@@ -7144,12 +7144,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15333</t>
+          <t>14301</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28610</t>
+          <t>28165</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10149</t>
+          <t>10059</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22433</t>
+          <t>22690</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>27405</t>
+          <t>27977</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>46968</t>
+          <t>46260</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,65%</t>
         </is>
       </c>
     </row>
@@ -7374,12 +7374,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>118369</t>
+          <t>118863</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>128628</t>
+          <t>128631</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7389,7 +7389,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>122802</t>
+          <t>121782</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>134653</t>
+          <t>134205</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>244414</t>
+          <t>244455</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>260929</t>
+          <t>260188</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,16%</t>
         </is>
       </c>
     </row>
@@ -7487,12 +7487,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7566</t>
+          <t>7563</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17825</t>
+          <t>17331</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8435</t>
+          <t>8883</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20286</t>
+          <t>21306</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18353</t>
+          <t>19094</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>34868</t>
+          <t>34827</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,47%</t>
         </is>
       </c>
     </row>
@@ -7717,12 +7717,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>49922</t>
+          <t>49973</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>57391</t>
+          <t>57548</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>60766</t>
+          <t>60931</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>67077</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>114211</t>
+          <t>113663</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>123272</t>
+          <t>123555</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,84%</t>
         </is>
       </c>
     </row>
@@ -7830,12 +7830,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3696</t>
+          <t>3539</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11165</t>
+          <t>11114</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>748</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7059</t>
+          <t>6894</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5640</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14701</t>
+          <t>15249</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,83%</t>
         </is>
       </c>
     </row>
@@ -8060,12 +8060,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>589905</t>
+          <t>589439</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>613995</t>
+          <t>614198</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>634913</t>
+          <t>632115</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>659523</t>
+          <t>658367</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1232980</t>
+          <t>1233596</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1267254</t>
+          <t>1268259</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,82%</t>
         </is>
       </c>
     </row>
@@ -8173,12 +8173,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>57507</t>
+          <t>57304</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>81597</t>
+          <t>82063</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>50214</t>
+          <t>51370</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>74824</t>
+          <t>77622</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>113985</t>
+          <t>112980</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>148259</t>
+          <t>147643</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,69%</t>
         </is>
       </c>
     </row>
